--- a/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_rf_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_rf_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>5586.225806451615</v>
       </c>
       <c r="I2" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J2" t="n">
-        <v>-2564.677426543311</v>
+        <v>-2620.598187673823</v>
       </c>
       <c r="K2" t="n">
-        <v>-523.2020023303039</v>
+        <v>-467.2812411997911</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>5164.951612903228</v>
       </c>
       <c r="I3" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J3" t="n">
-        <v>-2163.927823158858</v>
+        <v>-2219.848584289371</v>
       </c>
       <c r="K3" t="n">
-        <v>-122.4523989458512</v>
+        <v>-66.5316378153384</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>5488.701612903228</v>
       </c>
       <c r="I4" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J4" t="n">
-        <v>-2314.218806765415</v>
+        <v>-2370.139567895928</v>
       </c>
       <c r="K4" t="n">
-        <v>-272.7433825524085</v>
+        <v>-216.8226214218957</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>5265.903225806454</v>
       </c>
       <c r="I5" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J5" t="n">
-        <v>-2137.85484589815</v>
+        <v>-2193.775607028662</v>
       </c>
       <c r="K5" t="n">
-        <v>-96.37942168514292</v>
+        <v>-40.45866055463011</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>5812.782258064518</v>
       </c>
       <c r="I6" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J6" t="n">
-        <v>-2617.528960123426</v>
+        <v>-2673.449721253939</v>
       </c>
       <c r="K6" t="n">
-        <v>-576.0535359104197</v>
+        <v>-520.1327747799069</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>6148.08870967742</v>
       </c>
       <c r="I7" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J7" t="n">
-        <v>-2721.720657637968</v>
+        <v>-2777.64141876848</v>
       </c>
       <c r="K7" t="n">
-        <v>-680.245233424961</v>
+        <v>-624.3244722944482</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>6038.26612903226</v>
       </c>
       <c r="I8" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J8" t="n">
-        <v>-2550.225945845267</v>
+        <v>-2606.14670697578</v>
       </c>
       <c r="K8" t="n">
-        <v>-508.7505216322606</v>
+        <v>-452.8297605017478</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>5032.18548387097</v>
       </c>
       <c r="I9" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J9" t="n">
-        <v>-2004.686284290533</v>
+        <v>-2060.607045421046</v>
       </c>
       <c r="K9" t="n">
-        <v>36.78913992247317</v>
+        <v>92.70990105298597</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6432.564516129035</v>
       </c>
       <c r="I10" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J10" t="n">
-        <v>-2749.368595237123</v>
+        <v>-2805.289356367636</v>
       </c>
       <c r="K10" t="n">
-        <v>-707.8931710241168</v>
+        <v>-651.972409893604</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6457.548387096777</v>
       </c>
       <c r="I11" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J11" t="n">
-        <v>-2853.770498991751</v>
+        <v>-2909.691260122264</v>
       </c>
       <c r="K11" t="n">
-        <v>-812.2950747787445</v>
+        <v>-756.3743136482317</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>7444.741935483873</v>
       </c>
       <c r="I12" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J12" t="n">
-        <v>-3867.570604755896</v>
+        <v>-3923.491365886409</v>
       </c>
       <c r="K12" t="n">
-        <v>-1826.095180542889</v>
+        <v>-1770.174419412377</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6403.104838709679</v>
       </c>
       <c r="I13" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J13" t="n">
-        <v>-3143.433507981702</v>
+        <v>-3199.354269112215</v>
       </c>
       <c r="K13" t="n">
-        <v>-1101.958083768695</v>
+        <v>-1046.037322638183</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6240.346774193551</v>
       </c>
       <c r="I14" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J14" t="n">
-        <v>-2938.298394285246</v>
+        <v>-2994.219155415759</v>
       </c>
       <c r="K14" t="n">
-        <v>-896.8229700722395</v>
+        <v>-840.9022089417267</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>5061.258064516131</v>
       </c>
       <c r="I15" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J15" t="n">
-        <v>-1745.890012476678</v>
+        <v>-1801.810773607191</v>
       </c>
       <c r="K15" t="n">
-        <v>295.5854117363288</v>
+        <v>351.5061728668416</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>5416.137096774195</v>
       </c>
       <c r="I16" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J16" t="n">
-        <v>-1768.744454570808</v>
+        <v>-1824.665215701321</v>
       </c>
       <c r="K16" t="n">
-        <v>272.7309696421985</v>
+        <v>328.6517307727113</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>4892.532258064519</v>
       </c>
       <c r="I17" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J17" t="n">
-        <v>-1557.934697828345</v>
+        <v>-1613.855458958858</v>
       </c>
       <c r="K17" t="n">
-        <v>483.5407263846619</v>
+        <v>539.4614875151747</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>5486.927419354842</v>
       </c>
       <c r="I18" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J18" t="n">
-        <v>-1995.215105020307</v>
+        <v>-2051.13586615082</v>
       </c>
       <c r="K18" t="n">
-        <v>46.26031919269917</v>
+        <v>102.181080323212</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>5506.153225806454</v>
       </c>
       <c r="I19" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J19" t="n">
-        <v>-1868.563862291591</v>
+        <v>-1924.484623422104</v>
       </c>
       <c r="K19" t="n">
-        <v>172.9115619214153</v>
+        <v>228.8323230519281</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>5001.370967741937</v>
       </c>
       <c r="I20" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J20" t="n">
-        <v>-1490.69963701396</v>
+        <v>-1546.620398144473</v>
       </c>
       <c r="K20" t="n">
-        <v>550.7757871990461</v>
+        <v>606.6965483295589</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>4139.048387096776</v>
       </c>
       <c r="I21" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J21" t="n">
-        <v>-1020.737712106503</v>
+        <v>-1076.658473237016</v>
       </c>
       <c r="K21" t="n">
-        <v>1020.737712106503</v>
+        <v>1076.658473237016</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>5168.370967741937</v>
       </c>
       <c r="I22" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J22" t="n">
-        <v>-1496.69963701396</v>
+        <v>-1552.620398144473</v>
       </c>
       <c r="K22" t="n">
-        <v>544.7757871990461</v>
+        <v>600.6965483295589</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>4842.483870967743</v>
       </c>
       <c r="I23" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J23" t="n">
-        <v>-1362.55844187911</v>
+        <v>-1418.479203009623</v>
       </c>
       <c r="K23" t="n">
-        <v>678.9169823338962</v>
+        <v>734.837743464409</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>4789.806451612905</v>
       </c>
       <c r="I24" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J24" t="n">
-        <v>-1495.544956950502</v>
+        <v>-1551.465718081015</v>
       </c>
       <c r="K24" t="n">
-        <v>545.9304672625049</v>
+        <v>601.8512283930177</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>4081.201612903227</v>
       </c>
       <c r="I25" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J25" t="n">
-        <v>-1082.817167421152</v>
+        <v>-1138.737928551664</v>
       </c>
       <c r="K25" t="n">
-        <v>958.6582567918549</v>
+        <v>1014.579017922368</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>4269.35483870968</v>
       </c>
       <c r="I26" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J26" t="n">
-        <v>-1133.109737489899</v>
+        <v>-1189.030498620412</v>
       </c>
       <c r="K26" t="n">
-        <v>908.3656867231075</v>
+        <v>964.2864478536203</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>3495.161290322581</v>
       </c>
       <c r="I27" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J27" t="n">
-        <v>-357.1211071355879</v>
+        <v>-413.0418682661007</v>
       </c>
       <c r="K27" t="n">
-        <v>1684.354317077419</v>
+        <v>1740.275078207932</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>4251.040322580647</v>
       </c>
       <c r="I28" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J28" t="n">
-        <v>-931.3935820166043</v>
+        <v>-987.3143431471171</v>
       </c>
       <c r="K28" t="n">
-        <v>1110.081842196402</v>
+        <v>1166.002603326915</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>3719.741935483873</v>
       </c>
       <c r="I29" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J29" t="n">
-        <v>-620.9640473788463</v>
+        <v>-676.8848085093591</v>
       </c>
       <c r="K29" t="n">
-        <v>1420.51137683416</v>
+        <v>1476.432137964673</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>4514.717741935485</v>
       </c>
       <c r="I30" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J30" t="n">
-        <v>-1166.989034158327</v>
+        <v>-1222.90979528884</v>
       </c>
       <c r="K30" t="n">
-        <v>874.4863900546793</v>
+        <v>930.4071511851921</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>4403.282258064518</v>
       </c>
       <c r="I31" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J31" t="n">
-        <v>-934.2174847135902</v>
+        <v>-990.138245844103</v>
       </c>
       <c r="K31" t="n">
-        <v>1107.257939499416</v>
+        <v>1163.178700629929</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>4193.443548387098</v>
       </c>
       <c r="I32" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J32" t="n">
-        <v>-857.0427094624001</v>
+        <v>-912.9634705929129</v>
       </c>
       <c r="K32" t="n">
-        <v>1184.432714750606</v>
+        <v>1240.353475881119</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>3517.112903225808</v>
       </c>
       <c r="I33" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J33" t="n">
-        <v>-544.2858347929132</v>
+        <v>-600.206595923426</v>
       </c>
       <c r="K33" t="n">
-        <v>1497.189589420093</v>
+        <v>1553.110350550606</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>4273.379032258066</v>
       </c>
       <c r="I34" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J34" t="n">
-        <v>-832.1503244809087</v>
+        <v>-888.0710856114215</v>
       </c>
       <c r="K34" t="n">
-        <v>1209.325099732098</v>
+        <v>1265.245860862611</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>4310.774193548389</v>
       </c>
       <c r="I35" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J35" t="n">
-        <v>-896.4307316728709</v>
+        <v>-952.3514928033837</v>
       </c>
       <c r="K35" t="n">
-        <v>1145.044692540136</v>
+        <v>1200.965453670648</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>4445.008064516131</v>
       </c>
       <c r="I36" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J36" t="n">
-        <v>-1199.869520673399</v>
+        <v>-1255.790281803912</v>
       </c>
       <c r="K36" t="n">
-        <v>841.6059035396074</v>
+        <v>897.5266646701202</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>3772.064516129033</v>
       </c>
       <c r="I37" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J37" t="n">
-        <v>-824.9997427781054</v>
+        <v>-880.9205039086182</v>
       </c>
       <c r="K37" t="n">
-        <v>1216.475681434901</v>
+        <v>1272.396442565414</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>4061.209677419356</v>
       </c>
       <c r="I38" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J38" t="n">
-        <v>-873.8252319372809</v>
+        <v>-929.7459930677937</v>
       </c>
       <c r="K38" t="n">
-        <v>1167.650192275726</v>
+        <v>1223.570953406238</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>3636.879032258066</v>
       </c>
       <c r="I39" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J39" t="n">
-        <v>-449.0929474317281</v>
+        <v>-505.0137085622409</v>
       </c>
       <c r="K39" t="n">
-        <v>1592.382476781278</v>
+        <v>1648.303237911791</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>3519.209677419356</v>
       </c>
       <c r="I40" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J40" t="n">
-        <v>-387.4973630848217</v>
+        <v>-443.4181242153345</v>
       </c>
       <c r="K40" t="n">
-        <v>1653.978061128185</v>
+        <v>1709.898822258698</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>4019.733870967744</v>
       </c>
       <c r="I41" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J41" t="n">
-        <v>-759.0297533545208</v>
+        <v>-814.9505144850336</v>
       </c>
       <c r="K41" t="n">
-        <v>1282.445670858486</v>
+        <v>1338.366431988999</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>4195.104838709678</v>
       </c>
       <c r="I42" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J42" t="n">
-        <v>-900.6302292931764</v>
+        <v>-956.5509904236892</v>
       </c>
       <c r="K42" t="n">
-        <v>1140.84519491983</v>
+        <v>1196.765956050343</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>4034.18548387097</v>
       </c>
       <c r="I43" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J43" t="n">
-        <v>-700.4239892085661</v>
+        <v>-756.3447503390789</v>
       </c>
       <c r="K43" t="n">
-        <v>1341.05143500444</v>
+        <v>1396.972196134953</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>4392.814516129034</v>
       </c>
       <c r="I44" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J44" t="n">
-        <v>-958.8890870404011</v>
+        <v>-1014.809848170914</v>
       </c>
       <c r="K44" t="n">
-        <v>1082.586337172605</v>
+        <v>1138.507098303118</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>3261.483870967743</v>
       </c>
       <c r="I45" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J45" t="n">
-        <v>-310.4272943381266</v>
+        <v>-366.3480554686394</v>
       </c>
       <c r="K45" t="n">
-        <v>1731.04812987488</v>
+        <v>1786.968891005393</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>4223.274193548388</v>
       </c>
       <c r="I46" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J46" t="n">
-        <v>-758.3897480663127</v>
+        <v>-814.3105091968255</v>
       </c>
       <c r="K46" t="n">
-        <v>1283.085676146694</v>
+        <v>1339.006437277207</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>4679.314516129034</v>
       </c>
       <c r="I47" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J47" t="n">
-        <v>-1176.651382122368</v>
+        <v>-1232.572143252881</v>
       </c>
       <c r="K47" t="n">
-        <v>864.8240420906382</v>
+        <v>920.744803221151</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>4360.806451612905</v>
       </c>
       <c r="I48" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J48" t="n">
-        <v>-1161.7580717046</v>
+        <v>-1217.678832835113</v>
       </c>
       <c r="K48" t="n">
-        <v>879.7173525084063</v>
+        <v>935.6381136389191</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>4003.741935483873</v>
       </c>
       <c r="I49" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J49" t="n">
-        <v>-993.4886375427814</v>
+        <v>-1049.409398673294</v>
       </c>
       <c r="K49" t="n">
-        <v>1047.986786670225</v>
+        <v>1103.907547800738</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>4135.330645161293</v>
       </c>
       <c r="I50" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J50" t="n">
-        <v>-934.9871832857743</v>
+        <v>-990.9079444162871</v>
       </c>
       <c r="K50" t="n">
-        <v>1106.488240927232</v>
+        <v>1162.409002057745</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>3560.419354838711</v>
       </c>
       <c r="I51" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J51" t="n">
-        <v>-411.9447454222091</v>
+        <v>-467.8655065527219</v>
       </c>
       <c r="K51" t="n">
-        <v>1629.530678790798</v>
+        <v>1685.45143992131</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>3625.338709677421</v>
       </c>
       <c r="I52" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J52" t="n">
-        <v>-356.4132805887884</v>
+        <v>-412.3340417193012</v>
       </c>
       <c r="K52" t="n">
-        <v>1685.062143624218</v>
+        <v>1740.982904754731</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>3565.064516129034</v>
       </c>
       <c r="I53" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J53" t="n">
-        <v>-424.5653165485978</v>
+        <v>-480.4860776791106</v>
       </c>
       <c r="K53" t="n">
-        <v>1616.910107664409</v>
+        <v>1672.830868794922</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>4159.169354838711</v>
       </c>
       <c r="I54" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J54" t="n">
-        <v>-857.2111388648323</v>
+        <v>-913.1318999953451</v>
       </c>
       <c r="K54" t="n">
-        <v>1184.264285348174</v>
+        <v>1240.185046478687</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>4476.620967741937</v>
       </c>
       <c r="I55" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J55" t="n">
-        <v>-1037.457833735272</v>
+        <v>-1093.378594865785</v>
       </c>
       <c r="K55" t="n">
-        <v>1004.017590477735</v>
+        <v>1059.938351608248</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>4795.838709677422</v>
       </c>
       <c r="I56" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J56" t="n">
-        <v>-1321.69196911338</v>
+        <v>-1377.612730243893</v>
       </c>
       <c r="K56" t="n">
-        <v>719.7834550996267</v>
+        <v>775.7042162301395</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>3356.032258064518</v>
       </c>
       <c r="I57" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J57" t="n">
-        <v>-393.139615861131</v>
+        <v>-449.0603769916438</v>
       </c>
       <c r="K57" t="n">
-        <v>1648.335808351876</v>
+        <v>1704.256569482388</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>4715.120967741937</v>
       </c>
       <c r="I58" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J58" t="n">
-        <v>-1096.457833735272</v>
+        <v>-1152.378594865785</v>
       </c>
       <c r="K58" t="n">
-        <v>945.0175904777348</v>
+        <v>1000.938351608248</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>4700.120967741937</v>
       </c>
       <c r="I59" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J59" t="n">
-        <v>-1177.711932095927</v>
+        <v>-1233.63269322644</v>
       </c>
       <c r="K59" t="n">
-        <v>863.7634921170793</v>
+        <v>919.6842532475921</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>4286.68548387097</v>
       </c>
       <c r="I60" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J60" t="n">
-        <v>-1071.11251379873</v>
+        <v>-1127.033274929243</v>
       </c>
       <c r="K60" t="n">
-        <v>970.3629104142765</v>
+        <v>1026.283671544789</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>4158.629032258066</v>
       </c>
       <c r="I61" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J61" t="n">
-        <v>-1095.162619562876</v>
+        <v>-1151.083380693389</v>
       </c>
       <c r="K61" t="n">
-        <v>946.3128046501306</v>
+        <v>1002.233565780643</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>4054.741935483873</v>
       </c>
       <c r="I62" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J62" t="n">
-        <v>-911.5214244280269</v>
+        <v>-967.4421855585397</v>
       </c>
       <c r="K62" t="n">
-        <v>1129.95399978498</v>
+        <v>1185.874760915493</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>3745.451612903227</v>
       </c>
       <c r="I63" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J63" t="n">
-        <v>-589.0753641424635</v>
+        <v>-644.9961252729763</v>
       </c>
       <c r="K63" t="n">
-        <v>1452.400060070543</v>
+        <v>1508.320821201056</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>4277.983870967743</v>
       </c>
       <c r="I64" t="n">
-        <v>520.784546993114</v>
+        <v>549.3155475699061</v>
       </c>
       <c r="J64" t="n">
-        <v>-963.6322123709137</v>
+        <v>-1019.552973501427</v>
       </c>
       <c r="K64" t="n">
-        <v>1077.843211842093</v>
+        <v>1133.763972972606</v>
       </c>
     </row>
   </sheetData>
